--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/163.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/163.xlsx
@@ -426,13 +426,13 @@
         <v>-15.45243503611713</v>
       </c>
       <c r="E2">
-        <v>-6.453190749488053</v>
+        <v>-6.515271599659206</v>
       </c>
       <c r="F2">
-        <v>-5.840786398058112</v>
+        <v>-4.903318866472898</v>
       </c>
       <c r="G2">
-        <v>-2.079169413334367</v>
+        <v>-5.099201339352351</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-15.40251142742162</v>
       </c>
       <c r="E3">
-        <v>-5.956430736268638</v>
+        <v>-7.213711731284228</v>
       </c>
       <c r="F3">
-        <v>-4.964764675310357</v>
+        <v>-4.929670061923353</v>
       </c>
       <c r="G3">
-        <v>-3.067446709899759</v>
+        <v>-5.348677430100749</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-15.15212416672188</v>
       </c>
       <c r="E4">
-        <v>-6.152726499079125</v>
+        <v>-7.907166013026806</v>
       </c>
       <c r="F4">
-        <v>-5.041037432290524</v>
+        <v>-4.676859785895569</v>
       </c>
       <c r="G4">
-        <v>-3.65318484270855</v>
+        <v>-4.967183404337294</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-14.71930412980859</v>
       </c>
       <c r="E5">
-        <v>-9.133970377970774</v>
+        <v>-9.07251445721268</v>
       </c>
       <c r="F5">
-        <v>-5.074918487432427</v>
+        <v>-4.338292774492967</v>
       </c>
       <c r="G5">
-        <v>-3.541295024572262</v>
+        <v>-3.895678992914625</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-14.13368407665224</v>
       </c>
       <c r="E6">
-        <v>-10.35815728493831</v>
+        <v>-9.829127365940236</v>
       </c>
       <c r="F6">
-        <v>-5.450037210483558</v>
+        <v>-4.505844992322417</v>
       </c>
       <c r="G6">
-        <v>-2.754931210992559</v>
+        <v>-5.303405719851216</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-13.41453177635797</v>
       </c>
       <c r="E7">
-        <v>-9.040987221171278</v>
+        <v>-11.37630768150486</v>
       </c>
       <c r="F7">
-        <v>-5.275434757688881</v>
+        <v>-4.589878723499413</v>
       </c>
       <c r="G7">
-        <v>-3.429080772973126</v>
+        <v>-5.459348967478585</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-12.60196669790262</v>
       </c>
       <c r="E8">
-        <v>-10.45313297030118</v>
+        <v>-12.35137417636243</v>
       </c>
       <c r="F8">
-        <v>-4.670011672576626</v>
+        <v>-4.327454415394738</v>
       </c>
       <c r="G8">
-        <v>-2.688640847114193</v>
+        <v>-5.304531305334567</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-11.73039850001414</v>
       </c>
       <c r="E9">
-        <v>-13.05606813059205</v>
+        <v>-13.20476963158192</v>
       </c>
       <c r="F9">
-        <v>-5.381528741169831</v>
+        <v>-4.468283500809876</v>
       </c>
       <c r="G9">
-        <v>-2.523980933081923</v>
+        <v>-4.76220766672778</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-10.81718722036088</v>
       </c>
       <c r="E10">
-        <v>-12.67376982639051</v>
+        <v>-14.23123883490056</v>
       </c>
       <c r="F10">
-        <v>-4.520760575777225</v>
+        <v>-4.464208761555505</v>
       </c>
       <c r="G10">
-        <v>-3.11695260789402</v>
+        <v>-3.536835719730864</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-9.903513854597078</v>
       </c>
       <c r="E11">
-        <v>-13.91983831976311</v>
+        <v>-16.38251758308841</v>
       </c>
       <c r="F11">
-        <v>-5.080509139033921</v>
+        <v>-4.601022750169275</v>
       </c>
       <c r="G11">
-        <v>-2.071240656767813</v>
+        <v>-3.974152164377509</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-9.017741508309705</v>
       </c>
       <c r="E12">
-        <v>-15.16405466726657</v>
+        <v>-15.31959869248203</v>
       </c>
       <c r="F12">
-        <v>-4.535150145931255</v>
+        <v>-4.280548111211216</v>
       </c>
       <c r="G12">
-        <v>-1.521279589601926</v>
+        <v>-3.472700520998563</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-8.174438075522858</v>
       </c>
       <c r="E13">
-        <v>-14.84050878484054</v>
+        <v>-16.96305436544973</v>
       </c>
       <c r="F13">
-        <v>-4.666607910918523</v>
+        <v>-4.373104914595616</v>
       </c>
       <c r="G13">
-        <v>-1.650274996539628</v>
+        <v>-2.720292973015165</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-7.414579149271131</v>
       </c>
       <c r="E14">
-        <v>-17.02869459619091</v>
+        <v>-17.89546716362905</v>
       </c>
       <c r="F14">
-        <v>-4.705172555355854</v>
+        <v>-4.395021030971482</v>
       </c>
       <c r="G14">
-        <v>-0.9698453296710637</v>
+        <v>-1.516691173484496</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-6.758178931866455</v>
       </c>
       <c r="E15">
-        <v>-19.66080218603919</v>
+        <v>-19.60846208345853</v>
       </c>
       <c r="F15">
-        <v>-4.553043710199127</v>
+        <v>-4.686949300861667</v>
       </c>
       <c r="G15">
-        <v>-0.8605741530563397</v>
+        <v>-0.6613422119574605</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-6.211125209794429</v>
       </c>
       <c r="E16">
-        <v>-19.44314108286051</v>
+        <v>-20.35780226292977</v>
       </c>
       <c r="F16">
-        <v>-4.478355620060515</v>
+        <v>-4.486957387171185</v>
       </c>
       <c r="G16">
-        <v>1.070675624369518</v>
+        <v>-0.7517267262706424</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-5.793230825264845</v>
       </c>
       <c r="E17">
-        <v>-19.26044432749506</v>
+        <v>-21.03860851676892</v>
       </c>
       <c r="F17">
-        <v>-4.43965926520614</v>
+        <v>-3.867043671081759</v>
       </c>
       <c r="G17">
-        <v>1.973842105665787</v>
+        <v>0.357911859218892</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-5.496414050633865</v>
       </c>
       <c r="E18">
-        <v>-20.01945732744668</v>
+        <v>-22.1075502778055</v>
       </c>
       <c r="F18">
-        <v>-4.399181092068342</v>
+        <v>-3.788666032531078</v>
       </c>
       <c r="G18">
-        <v>2.511428353605877</v>
+        <v>0.3626922869775995</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-5.300512193512712</v>
       </c>
       <c r="E19">
-        <v>-21.41618815105447</v>
+        <v>-23.2635202523215</v>
       </c>
       <c r="F19">
-        <v>-4.72358219251567</v>
+        <v>-4.104420634027985</v>
       </c>
       <c r="G19">
-        <v>2.390576888694783</v>
+        <v>1.561977135125058</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-5.196280439982393</v>
       </c>
       <c r="E20">
-        <v>-20.71336445659002</v>
+        <v>-23.48129909582437</v>
       </c>
       <c r="F20">
-        <v>-4.049875125655846</v>
+        <v>-3.511962327136945</v>
       </c>
       <c r="G20">
-        <v>3.523376050777058</v>
+        <v>2.01025810659777</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-5.157028816430038</v>
       </c>
       <c r="E21">
-        <v>-22.62258268364587</v>
+        <v>-24.12511677396887</v>
       </c>
       <c r="F21">
-        <v>-4.550526301662019</v>
+        <v>-3.634559874383869</v>
       </c>
       <c r="G21">
-        <v>2.591930889484335</v>
+        <v>2.38109548627031</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-5.15769815587479</v>
       </c>
       <c r="E22">
-        <v>-22.56684622555946</v>
+        <v>-25.10899567924537</v>
       </c>
       <c r="F22">
-        <v>-3.792366349719383</v>
+        <v>-3.536418217969795</v>
       </c>
       <c r="G22">
-        <v>3.668887769410184</v>
+        <v>2.062197255563395</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-5.187908679944571</v>
       </c>
       <c r="E23">
-        <v>-24.28844977447753</v>
+        <v>-26.20646229805627</v>
       </c>
       <c r="F23">
-        <v>-3.760739282280498</v>
+        <v>-3.358465847398197</v>
       </c>
       <c r="G23">
-        <v>3.731175683731572</v>
+        <v>3.410393752612811</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-5.229441472597994</v>
       </c>
       <c r="E24">
-        <v>-24.14777725790325</v>
+        <v>-25.93050614897685</v>
       </c>
       <c r="F24">
-        <v>-3.478984192464094</v>
+        <v>-3.084011987870067</v>
       </c>
       <c r="G24">
-        <v>3.147870801894145</v>
+        <v>2.976457374961762</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-5.271686427934781</v>
       </c>
       <c r="E25">
-        <v>-24.26799465738488</v>
+        <v>-25.90035104055977</v>
       </c>
       <c r="F25">
-        <v>-3.120769134634489</v>
+        <v>-3.304141513122605</v>
       </c>
       <c r="G25">
-        <v>2.744060388650464</v>
+        <v>3.001355987962621</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-5.316428594269722</v>
       </c>
       <c r="E26">
-        <v>-24.10521413070516</v>
+        <v>-26.42215804351562</v>
       </c>
       <c r="F26">
-        <v>-3.128487862093775</v>
+        <v>-3.304795923370817</v>
       </c>
       <c r="G26">
-        <v>3.343838545091304</v>
+        <v>3.146510167677505</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-5.359690259019217</v>
       </c>
       <c r="E27">
-        <v>-23.46686232068792</v>
+        <v>-26.21795103661373</v>
       </c>
       <c r="F27">
-        <v>-3.556477134628585</v>
+        <v>-3.445827130432238</v>
       </c>
       <c r="G27">
-        <v>3.235219545947816</v>
+        <v>3.321515536519998</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-5.404551920592114</v>
       </c>
       <c r="E28">
-        <v>-24.91391807594295</v>
+        <v>-26.73679188909454</v>
       </c>
       <c r="F28">
-        <v>-2.469275568048137</v>
+        <v>-2.985069300177486</v>
       </c>
       <c r="G28">
-        <v>1.973345523834896</v>
+        <v>2.964370573197883</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-5.462275905899088</v>
       </c>
       <c r="E29">
-        <v>-24.25675045642383</v>
+        <v>-26.13799177106029</v>
       </c>
       <c r="F29">
-        <v>-3.452132663102348</v>
+        <v>-3.157829463868337</v>
       </c>
       <c r="G29">
-        <v>3.421076883068039</v>
+        <v>2.317029808994334</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-5.535449557655324</v>
       </c>
       <c r="E30">
-        <v>-23.90942555698353</v>
+        <v>-24.59093372429388</v>
       </c>
       <c r="F30">
-        <v>-3.260923928983749</v>
+        <v>-3.13523574295698</v>
       </c>
       <c r="G30">
-        <v>2.735161642240903</v>
+        <v>3.482159758813132</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-5.632087693799527</v>
       </c>
       <c r="E31">
-        <v>-24.76955938152643</v>
+        <v>-25.41269326009578</v>
       </c>
       <c r="F31">
-        <v>-3.221661799193261</v>
+        <v>-3.058067520814387</v>
       </c>
       <c r="G31">
-        <v>2.527030954732463</v>
+        <v>2.505469371635189</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-5.763631872906537</v>
       </c>
       <c r="E32">
-        <v>-24.81803669577854</v>
+        <v>-24.59889931007337</v>
       </c>
       <c r="F32">
-        <v>-3.302988425697908</v>
+        <v>-3.218137095894349</v>
       </c>
       <c r="G32">
-        <v>3.775626378687366</v>
+        <v>2.421725811673785</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-5.928786392064326</v>
       </c>
       <c r="E33">
-        <v>-21.75397155576061</v>
+        <v>-24.72781590812373</v>
       </c>
       <c r="F33">
-        <v>-2.702875175637598</v>
+        <v>-3.382350993090518</v>
       </c>
       <c r="G33">
-        <v>2.902264738881156</v>
+        <v>1.89156511737828</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-6.132486642808447</v>
       </c>
       <c r="E34">
-        <v>-23.79200675443865</v>
+        <v>-24.75716947664145</v>
       </c>
       <c r="F34">
-        <v>-3.902534244087301</v>
+        <v>-3.512640760039838</v>
       </c>
       <c r="G34">
-        <v>2.846899175282384</v>
+        <v>2.592036826941592</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-6.378411187640565</v>
       </c>
       <c r="E35">
-        <v>-21.47401223565841</v>
+        <v>-23.50471130644403</v>
       </c>
       <c r="F35">
-        <v>-3.228501628838177</v>
+        <v>-3.079425317560766</v>
       </c>
       <c r="G35">
-        <v>3.18555143122213</v>
+        <v>2.219941439964128</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-6.654848287467449</v>
       </c>
       <c r="E36">
-        <v>-20.76606683709129</v>
+        <v>-23.25199981444598</v>
       </c>
       <c r="F36">
-        <v>-2.819524216565019</v>
+        <v>-3.177682945411232</v>
       </c>
       <c r="G36">
-        <v>1.902470054384639</v>
+        <v>1.384601415676447</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-6.961038877064717</v>
       </c>
       <c r="E37">
-        <v>-21.79876722064449</v>
+        <v>-22.82712479762433</v>
       </c>
       <c r="F37">
-        <v>-3.032262219482377</v>
+        <v>-3.219017650443525</v>
       </c>
       <c r="G37">
-        <v>1.466931372692583</v>
+        <v>1.267964275236845</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-7.293216607471058</v>
       </c>
       <c r="E38">
-        <v>-20.97649596727972</v>
+        <v>-20.76082286419041</v>
       </c>
       <c r="F38">
-        <v>-2.883911558049819</v>
+        <v>-3.423166311761255</v>
       </c>
       <c r="G38">
-        <v>2.923203939417046</v>
+        <v>1.155842718912808</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-7.633896634619056</v>
       </c>
       <c r="E39">
-        <v>-19.74135015321362</v>
+        <v>-19.90167171850717</v>
       </c>
       <c r="F39">
-        <v>-3.017986964029932</v>
+        <v>-3.249847000073514</v>
       </c>
       <c r="G39">
-        <v>1.632253395832707</v>
+        <v>0.9713956741923141</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-7.982918358293549</v>
       </c>
       <c r="E40">
-        <v>-18.42189773854672</v>
+        <v>-20.32013441613397</v>
       </c>
       <c r="F40">
-        <v>-2.891124153025994</v>
+        <v>-3.275339178527266</v>
       </c>
       <c r="G40">
-        <v>1.670291564078933</v>
+        <v>0.2051997040378513</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-8.335229394536997</v>
       </c>
       <c r="E41">
-        <v>-18.72062758341071</v>
+        <v>-19.70339701255534</v>
       </c>
       <c r="F41">
-        <v>-2.754068281130607</v>
+        <v>-2.969613621176053</v>
       </c>
       <c r="G41">
-        <v>1.123137839530348</v>
+        <v>-0.6708534092917865</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-8.674157864932676</v>
       </c>
       <c r="E42">
-        <v>-17.06998069371884</v>
+        <v>-17.95292444183837</v>
       </c>
       <c r="F42">
-        <v>-3.077105060465525</v>
+        <v>-3.42562987641718</v>
       </c>
       <c r="G42">
-        <v>0.4646372263139165</v>
+        <v>0.1199663985837754</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-9.004898999428516</v>
       </c>
       <c r="E43">
-        <v>-16.75542383219804</v>
+        <v>-17.13755005438729</v>
       </c>
       <c r="F43">
-        <v>-2.600878297330895</v>
+        <v>-3.106762270220553</v>
       </c>
       <c r="G43">
-        <v>-0.09296126941106884</v>
+        <v>0.1233067390329</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-9.324391303932153</v>
       </c>
       <c r="E44">
-        <v>-15.81294423629966</v>
+        <v>-16.77579743675855</v>
       </c>
       <c r="F44">
-        <v>-2.479582943641172</v>
+        <v>-2.760911424245134</v>
       </c>
       <c r="G44">
-        <v>-0.06577506944257386</v>
+        <v>-1.636827560559108</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-9.619828568755992</v>
       </c>
       <c r="E45">
-        <v>-14.6597049316103</v>
+        <v>-15.43428682520029</v>
       </c>
       <c r="F45">
-        <v>-2.775756596470704</v>
+        <v>-2.760698533822615</v>
       </c>
       <c r="G45">
-        <v>0.2555663438723232</v>
+        <v>-1.308643249614538</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-9.899821344310366</v>
       </c>
       <c r="E46">
-        <v>-14.33514919948056</v>
+        <v>-14.27935839970606</v>
       </c>
       <c r="F46">
-        <v>-2.831620037380697</v>
+        <v>-2.609272144223462</v>
       </c>
       <c r="G46">
-        <v>-0.9830312325539809</v>
+        <v>-1.206555956820032</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-10.16076918334223</v>
       </c>
       <c r="E47">
-        <v>-13.10483979565466</v>
+        <v>-13.69494977206819</v>
       </c>
       <c r="F47">
-        <v>-2.424634020343869</v>
+        <v>-2.780462551686008</v>
       </c>
       <c r="G47">
-        <v>-1.904948643784682</v>
+        <v>-2.203695583794053</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-10.3943917077687</v>
       </c>
       <c r="E48">
-        <v>-10.57910606024655</v>
+        <v>-13.69269006353836</v>
       </c>
       <c r="F48">
-        <v>-2.482526961390721</v>
+        <v>-2.788752024285822</v>
       </c>
       <c r="G48">
-        <v>-0.8839631572912906</v>
+        <v>-2.521200074828935</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-10.61070617102937</v>
       </c>
       <c r="E49">
-        <v>-10.24683833688176</v>
+        <v>-12.94783307333472</v>
       </c>
       <c r="F49">
-        <v>-2.18668796899192</v>
+        <v>-2.34370335345776</v>
       </c>
       <c r="G49">
-        <v>-1.27783531282608</v>
+        <v>-2.077623388567527</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-10.80544677641413</v>
       </c>
       <c r="E50">
-        <v>-10.5499698584812</v>
+        <v>-11.94383415804214</v>
       </c>
       <c r="F50">
-        <v>-2.415387783393821</v>
+        <v>-2.917705634614427</v>
       </c>
       <c r="G50">
-        <v>-1.113549490439747</v>
+        <v>-2.471723971744527</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-10.97393759677155</v>
       </c>
       <c r="E51">
-        <v>-8.431717271231294</v>
+        <v>-10.25337745334883</v>
       </c>
       <c r="F51">
-        <v>-2.399298403329246</v>
+        <v>-2.505622672948174</v>
       </c>
       <c r="G51">
-        <v>-3.361078857050956</v>
+        <v>-3.402510334474935</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-11.12510400489201</v>
       </c>
       <c r="E52">
-        <v>-9.896823523880899</v>
+        <v>-9.401621305720123</v>
       </c>
       <c r="F52">
-        <v>-2.208905611102405</v>
+        <v>-1.952998897722957</v>
       </c>
       <c r="G52">
-        <v>-3.742774826092306</v>
+        <v>-3.739315306003768</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-11.25152895587761</v>
       </c>
       <c r="E53">
-        <v>-8.839755421692431</v>
+        <v>-9.422560969531592</v>
       </c>
       <c r="F53">
-        <v>-2.425032465064616</v>
+        <v>-2.523608185997757</v>
       </c>
       <c r="G53">
-        <v>-2.987103080207187</v>
+        <v>-4.184802177041335</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-11.35075099613957</v>
       </c>
       <c r="E54">
-        <v>-7.51560697947958</v>
+        <v>-9.45282928979886</v>
       </c>
       <c r="F54">
-        <v>-2.414677044162219</v>
+        <v>-2.363696829091729</v>
       </c>
       <c r="G54">
-        <v>-2.700836896880868</v>
+        <v>-5.58069370367503</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-11.42843561083536</v>
       </c>
       <c r="E55">
-        <v>-5.963377415396404</v>
+        <v>-9.242694510420932</v>
       </c>
       <c r="F55">
-        <v>-1.904846728965624</v>
+        <v>-2.265268557556286</v>
       </c>
       <c r="G55">
-        <v>-3.363101600375451</v>
+        <v>-4.11246344646272</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-11.47386594864163</v>
       </c>
       <c r="E56">
-        <v>-6.424715704927822</v>
+        <v>-8.045601463441288</v>
       </c>
       <c r="F56">
-        <v>-2.420079656363277</v>
+        <v>-2.567305394862834</v>
       </c>
       <c r="G56">
-        <v>-3.958688606163573</v>
+        <v>-4.803433890328323</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-11.48857187692721</v>
       </c>
       <c r="E57">
-        <v>-4.941875948064179</v>
+        <v>-7.366742453425433</v>
       </c>
       <c r="F57">
-        <v>-2.732518303146778</v>
+        <v>-2.238851092713607</v>
       </c>
       <c r="G57">
-        <v>-3.632374753448691</v>
+        <v>-4.897648705830442</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-11.47833488724349</v>
       </c>
       <c r="E58">
-        <v>-5.510729267485706</v>
+        <v>-5.586875557924683</v>
       </c>
       <c r="F58">
-        <v>-2.286024959568234</v>
+        <v>-2.380562389412727</v>
       </c>
       <c r="G58">
-        <v>-4.957523232453701</v>
+        <v>-5.340934064084394</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-11.43338964754891</v>
       </c>
       <c r="E59">
-        <v>-3.449309029032059</v>
+        <v>-6.577692085380934</v>
       </c>
       <c r="F59">
-        <v>-2.21967770080841</v>
+        <v>-2.889513806794952</v>
       </c>
       <c r="G59">
-        <v>-4.360830504455462</v>
+        <v>-5.654644669931271</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-11.36154174595737</v>
       </c>
       <c r="E60">
-        <v>-3.691682014870592</v>
+        <v>-6.093036683184022</v>
       </c>
       <c r="F60">
-        <v>-2.559979313552475</v>
+        <v>-2.414435160880601</v>
       </c>
       <c r="G60">
-        <v>-3.540954038381717</v>
+        <v>-5.62634943720712</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-11.26820372073027</v>
       </c>
       <c r="E61">
-        <v>-5.558264659144221</v>
+        <v>-5.755778581462772</v>
       </c>
       <c r="F61">
-        <v>-2.366490912341372</v>
+        <v>-2.647039070851897</v>
       </c>
       <c r="G61">
-        <v>-4.293772094011985</v>
+        <v>-5.832543455575086</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-11.14312314523902</v>
       </c>
       <c r="E62">
-        <v>-1.459171499933152</v>
+        <v>-5.48578190417745</v>
       </c>
       <c r="F62">
-        <v>-2.639573823817868</v>
+        <v>-2.308205325145593</v>
       </c>
       <c r="G62">
-        <v>-4.886058485897454</v>
+        <v>-5.423631491655388</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-10.99892265462719</v>
       </c>
       <c r="E63">
-        <v>-4.125247173312967</v>
+        <v>-5.108007545509573</v>
       </c>
       <c r="F63">
-        <v>-3.277859072166582</v>
+        <v>-2.251382634783158</v>
       </c>
       <c r="G63">
-        <v>-4.846898042713415</v>
+        <v>-5.773774651161944</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-10.83864918175633</v>
       </c>
       <c r="E64">
-        <v>-2.750583603544554</v>
+        <v>-3.683209240002241</v>
       </c>
       <c r="F64">
-        <v>-2.79227838431954</v>
+        <v>-2.65329241637563</v>
       </c>
       <c r="G64">
-        <v>-4.815547176456517</v>
+        <v>-5.473425407111566</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-10.65229528276685</v>
       </c>
       <c r="E65">
-        <v>-2.438200409547437</v>
+        <v>-4.206465354640535</v>
       </c>
       <c r="F65">
-        <v>-2.946622283911352</v>
+        <v>-2.47298996748229</v>
       </c>
       <c r="G65">
-        <v>-4.879059992627434</v>
+        <v>-5.891884984366522</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-10.45213043371143</v>
       </c>
       <c r="E66">
-        <v>-1.373329746643753</v>
+        <v>-4.000958675698447</v>
       </c>
       <c r="F66">
-        <v>-2.844513576005271</v>
+        <v>-2.540858937161056</v>
       </c>
       <c r="G66">
-        <v>-4.23906201842999</v>
+        <v>-5.27867594467286</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-10.23532906037053</v>
       </c>
       <c r="E67">
-        <v>-1.537020496599013</v>
+        <v>-4.143691647946209</v>
       </c>
       <c r="F67">
-        <v>-2.904356493918313</v>
+        <v>-2.883513113329072</v>
       </c>
       <c r="G67">
-        <v>-3.270575163098361</v>
+        <v>-5.247202588231008</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-9.991055460020535</v>
       </c>
       <c r="E68">
-        <v>-1.248253294551898</v>
+        <v>-3.931283574616431</v>
       </c>
       <c r="F68">
-        <v>-2.96153206879434</v>
+        <v>-2.670515003047235</v>
       </c>
       <c r="G68">
-        <v>-2.887925756941701</v>
+        <v>-5.004205235102964</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-9.727429939159389</v>
       </c>
       <c r="E69">
-        <v>-1.260140538822032</v>
+        <v>-4.298212238035937</v>
       </c>
       <c r="F69">
-        <v>-2.794840524696399</v>
+        <v>-2.594600100785077</v>
       </c>
       <c r="G69">
-        <v>-3.975519419685228</v>
+        <v>-5.178303514467697</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-9.436613908052731</v>
       </c>
       <c r="E70">
-        <v>-2.832182176688766</v>
+        <v>-2.822749365330789</v>
       </c>
       <c r="F70">
-        <v>-2.90049713018867</v>
+        <v>-2.67637238895243</v>
       </c>
       <c r="G70">
-        <v>-4.483959624697575</v>
+        <v>-5.0767227351407</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-9.109459227521839</v>
       </c>
       <c r="E71">
-        <v>-2.299692503548832</v>
+        <v>-3.448806368417208</v>
       </c>
       <c r="F71">
-        <v>-2.705742155218687</v>
+        <v>-2.927119201779841</v>
       </c>
       <c r="G71">
-        <v>-3.276693051254934</v>
+        <v>-4.006830559395655</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-8.750581270278332</v>
       </c>
       <c r="E72">
-        <v>-3.074632146585429</v>
+        <v>-4.118237095549094</v>
       </c>
       <c r="F72">
-        <v>-3.026119046823215</v>
+        <v>-2.834213655718862</v>
       </c>
       <c r="G72">
-        <v>-3.207353674934899</v>
+        <v>-4.116664528752055</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-8.351324907040848</v>
       </c>
       <c r="E73">
-        <v>-3.312404202832169</v>
+        <v>-3.83191526946612</v>
       </c>
       <c r="F73">
-        <v>-3.299365146678063</v>
+        <v>-2.721513442200587</v>
       </c>
       <c r="G73">
-        <v>-2.494527009419027</v>
+        <v>-3.373831078468229</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-7.909341505022932</v>
       </c>
       <c r="E74">
-        <v>-1.553716980265294</v>
+        <v>-4.529481405607663</v>
       </c>
       <c r="F74">
-        <v>-3.380029079260471</v>
+        <v>-2.617712379690586</v>
       </c>
       <c r="G74">
-        <v>-2.884456305216544</v>
+        <v>-2.942228635422366</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-7.431635712700749</v>
       </c>
       <c r="E75">
-        <v>-4.161868942612998</v>
+        <v>-4.116163054453581</v>
       </c>
       <c r="F75">
-        <v>-3.475308726297873</v>
+        <v>-2.285324989112868</v>
       </c>
       <c r="G75">
-        <v>-2.756463993577241</v>
+        <v>-2.747545383894445</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-6.916198992472382</v>
       </c>
       <c r="E76">
-        <v>-2.191380462233372</v>
+        <v>-6.148438034193861</v>
       </c>
       <c r="F76">
-        <v>-3.224830304508969</v>
+        <v>-2.78725102255195</v>
       </c>
       <c r="G76">
-        <v>-0.9793830113697041</v>
+        <v>-2.166253313744896</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-6.371727611648275</v>
       </c>
       <c r="E77">
-        <v>-5.18473800909554</v>
+        <v>-4.887443690491981</v>
       </c>
       <c r="F77">
-        <v>-3.295441998658405</v>
+        <v>-2.987203174607097</v>
       </c>
       <c r="G77">
-        <v>-1.712092813394439</v>
+        <v>-2.068565735972081</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-5.812356525314543</v>
       </c>
       <c r="E78">
-        <v>-4.590824114515565</v>
+        <v>-7.235738228857537</v>
       </c>
       <c r="F78">
-        <v>-3.565544444219628</v>
+        <v>-3.447031576635908</v>
       </c>
       <c r="G78">
-        <v>-0.9699280933095455</v>
+        <v>-1.879867950779163</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-5.244633309459599</v>
       </c>
       <c r="E79">
-        <v>-4.64147056781735</v>
+        <v>-6.374105479418098</v>
       </c>
       <c r="F79">
-        <v>-3.55048969504115</v>
+        <v>-3.562039621738383</v>
       </c>
       <c r="G79">
-        <v>0.2339617236830394</v>
+        <v>-1.871128110555487</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-4.687052664914948</v>
       </c>
       <c r="E80">
-        <v>-5.291238660807932</v>
+        <v>-6.8640093829899</v>
       </c>
       <c r="F80">
-        <v>-3.60550902956769</v>
+        <v>-2.859217925772365</v>
       </c>
       <c r="G80">
-        <v>1.212999287648325</v>
+        <v>-0.7537660223228334</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-4.158224805836136</v>
       </c>
       <c r="E81">
-        <v>-6.471820891555609</v>
+        <v>-7.587614244675547</v>
       </c>
       <c r="F81">
-        <v>-4.147279535081428</v>
+        <v>-3.44649065272188</v>
       </c>
       <c r="G81">
-        <v>1.378404074426932</v>
+        <v>-0.7901787127092772</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-3.668249288926984</v>
       </c>
       <c r="E82">
-        <v>-7.34120638849618</v>
+        <v>-9.58131568281849</v>
       </c>
       <c r="F82">
-        <v>-3.654572402468102</v>
+        <v>-2.845013081549159</v>
       </c>
       <c r="G82">
-        <v>0.9744215128152081</v>
+        <v>0.1084026630151011</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-3.237791149553062</v>
       </c>
       <c r="E83">
-        <v>-9.473488188221852</v>
+        <v>-9.519995616280626</v>
       </c>
       <c r="F83">
-        <v>-4.128640440151037</v>
+        <v>-3.683268706035883</v>
       </c>
       <c r="G83">
-        <v>2.309044773153612</v>
+        <v>1.208367834438885</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-2.883444747554682</v>
       </c>
       <c r="E84">
-        <v>-8.981700439462859</v>
+        <v>-11.2825773264941</v>
       </c>
       <c r="F84">
-        <v>-3.702226722416352</v>
+        <v>-3.637580101934476</v>
       </c>
       <c r="G84">
-        <v>0.9133055316147226</v>
+        <v>0.5545715064337575</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-2.610894532158675</v>
       </c>
       <c r="E85">
-        <v>-11.46156526164727</v>
+        <v>-11.97801055137803</v>
       </c>
       <c r="F85">
-        <v>-4.312769118077909</v>
+        <v>-3.825676659720757</v>
       </c>
       <c r="G85">
-        <v>2.029677766731135</v>
+        <v>1.91849971588579</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-2.435501641380796</v>
       </c>
       <c r="E86">
-        <v>-13.88982812251428</v>
+        <v>-13.18241708388006</v>
       </c>
       <c r="F86">
-        <v>-4.246875804654819</v>
+        <v>-4.110726166698095</v>
       </c>
       <c r="G86">
-        <v>1.082106938116621</v>
+        <v>2.035398389422995</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-2.365655543838499</v>
       </c>
       <c r="E87">
-        <v>-13.92228369572725</v>
+        <v>-14.12683033817971</v>
       </c>
       <c r="F87">
-        <v>-4.136679745795206</v>
+        <v>-4.037214358271458</v>
       </c>
       <c r="G87">
-        <v>2.729623099553702</v>
+        <v>1.709170610892134</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-2.397131551990813</v>
       </c>
       <c r="E88">
-        <v>-14.14685072176762</v>
+        <v>-15.59413290072304</v>
       </c>
       <c r="F88">
-        <v>-4.171433071812257</v>
+        <v>-3.666905964728384</v>
       </c>
       <c r="G88">
-        <v>2.407493776400459</v>
+        <v>2.420772374558475</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-2.536639124677583</v>
       </c>
       <c r="E89">
-        <v>-17.7143055609522</v>
+        <v>-16.90510801204757</v>
       </c>
       <c r="F89">
-        <v>-4.471174503045646</v>
+        <v>-4.224876023171269</v>
       </c>
       <c r="G89">
-        <v>3.137717358725201</v>
+        <v>2.172885345668928</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-2.78263999547761</v>
       </c>
       <c r="E90">
-        <v>-17.73395008119747</v>
+        <v>-17.44336243259928</v>
       </c>
       <c r="F90">
-        <v>-4.786768401266411</v>
+        <v>-3.865763843444433</v>
       </c>
       <c r="G90">
-        <v>2.03133303950077</v>
+        <v>2.177874337796609</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-3.120815718611094</v>
       </c>
       <c r="E91">
-        <v>-19.92463108172606</v>
+        <v>-20.11851316789046</v>
       </c>
       <c r="F91">
-        <v>-4.70937320645545</v>
+        <v>-4.305221862671002</v>
       </c>
       <c r="G91">
-        <v>2.941507945703676</v>
+        <v>2.140342683017892</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-3.549681380312248</v>
       </c>
       <c r="E92">
-        <v>-21.13040521337841</v>
+        <v>-22.37861567495664</v>
       </c>
       <c r="F92">
-        <v>-4.297128713145651</v>
+        <v>-3.941801344082206</v>
       </c>
       <c r="G92">
-        <v>2.02215951781145</v>
+        <v>1.916357792921882</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-4.060751509877494</v>
       </c>
       <c r="E93">
-        <v>-23.29492974803869</v>
+        <v>-24.64066542584611</v>
       </c>
       <c r="F93">
-        <v>-4.256846034714914</v>
+        <v>-3.935672253668892</v>
       </c>
       <c r="G93">
-        <v>1.471903812092568</v>
+        <v>2.06004209041733</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-4.633513145628601</v>
       </c>
       <c r="E94">
-        <v>-25.62945319694693</v>
+        <v>-26.15748685166331</v>
       </c>
       <c r="F94">
-        <v>-3.968429214245196</v>
+        <v>-4.127124527803914</v>
       </c>
       <c r="G94">
-        <v>0.7318048724241798</v>
+        <v>1.792414278477108</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-5.262443661391933</v>
       </c>
       <c r="E95">
-        <v>-27.58254328018908</v>
+        <v>-27.90508836985941</v>
       </c>
       <c r="F95">
-        <v>-4.496729637422011</v>
+        <v>-4.565977010459036</v>
       </c>
       <c r="G95">
-        <v>0.9555712665145979</v>
+        <v>0.801524961481231</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-5.939537800111737</v>
       </c>
       <c r="E96">
-        <v>-30.28155454502668</v>
+        <v>-29.48719227697119</v>
       </c>
       <c r="F96">
-        <v>-4.971949105794837</v>
+        <v>-4.518955563206525</v>
       </c>
       <c r="G96">
-        <v>0.06036664724027618</v>
+        <v>1.318989713633632</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-6.636412297903585</v>
       </c>
       <c r="E97">
-        <v>-31.08692779763183</v>
+        <v>-32.61302580245374</v>
       </c>
       <c r="F97">
-        <v>-4.982060158313408</v>
+        <v>-4.553924264748303</v>
       </c>
       <c r="G97">
-        <v>-0.7307842151892129</v>
+        <v>1.020775771456083</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-7.361046047727384</v>
       </c>
       <c r="E98">
-        <v>-36.08993833232896</v>
+        <v>-35.21423334991069</v>
       </c>
       <c r="F98">
-        <v>-4.545418588256358</v>
+        <v>-4.769573979086501</v>
       </c>
       <c r="G98">
-        <v>-0.5961112226516609</v>
+        <v>-0.2907564337459045</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-8.07756063798265</v>
       </c>
       <c r="E99">
-        <v>-36.0066551668539</v>
+        <v>-36.34492764675286</v>
       </c>
       <c r="F99">
-        <v>-5.277304382916999</v>
+        <v>-4.632464263309933</v>
       </c>
       <c r="G99">
-        <v>-0.2815564276922699</v>
+        <v>0.2778727997159324</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-8.800274295239918</v>
       </c>
       <c r="E100">
-        <v>-39.4614800647567</v>
+        <v>-39.92947521107939</v>
       </c>
       <c r="F100">
-        <v>-4.957966264035582</v>
+        <v>-4.765889400878849</v>
       </c>
       <c r="G100">
-        <v>-1.829358957486503</v>
+        <v>-1.188420788355905</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-9.469166702157802</v>
       </c>
       <c r="E101">
-        <v>-42.69333875218084</v>
+        <v>-41.18442630621804</v>
       </c>
       <c r="F101">
-        <v>-5.070368265288849</v>
+        <v>-4.781579507855274</v>
       </c>
       <c r="G101">
-        <v>-1.345631974924815</v>
+        <v>-0.9277716064124663</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-10.16140793848423</v>
       </c>
       <c r="E102">
-        <v>-44.15084396120857</v>
+        <v>-44.37813712860157</v>
       </c>
       <c r="F102">
-        <v>-5.466965726727168</v>
+        <v>-5.035028455150616</v>
       </c>
       <c r="G102">
-        <v>-2.679013780685992</v>
+        <v>-1.265559809966463</v>
       </c>
     </row>
   </sheetData>
